--- a/IaR_GaR_April_2026/Outputs/semi-param_best_spec_gdp_OOS.xlsx
+++ b/IaR_GaR_April_2026/Outputs/semi-param_best_spec_gdp_OOS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="84" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="42" uniqueCount="14">
   <si>
     <t>Dates</t>
   </si>
@@ -170,43 +170,43 @@
         <v>46112</v>
       </c>
       <c r="B2" s="0">
-        <v>0.98103019917876755</v>
+        <v>0.98138547631443074</v>
       </c>
       <c r="C2" s="0">
-        <v>1.3682052033888912</v>
+        <v>1.3680843758611727</v>
       </c>
       <c r="D2" s="0">
-        <v>1.7514474657248829</v>
+        <v>1.7461611119148086</v>
       </c>
       <c r="E2" s="0">
-        <v>2.2635542500652917</v>
+        <v>2.2540715048482345</v>
       </c>
       <c r="F2" s="0">
-        <v>2.6356260372715878</v>
+        <v>2.6273827173588407</v>
       </c>
       <c r="G2" s="0">
-        <v>2.7179057563203006</v>
+        <v>2.7014903348626014</v>
       </c>
       <c r="H2" s="0">
-        <v>2.5684133641832743</v>
+        <v>2.5527770586140219</v>
       </c>
       <c r="I2" s="0">
-        <v>2.2870305246770362</v>
+        <v>2.2742555022553135</v>
       </c>
       <c r="J2" s="0">
-        <v>2.1755355535717578</v>
+        <v>2.1554624126910871</v>
       </c>
       <c r="K2" s="0">
-        <v>2.3858434707379375</v>
+        <v>2.3745494448079034</v>
       </c>
       <c r="L2" s="0">
-        <v>2.4722059375123377</v>
+        <v>2.4454299494010687</v>
       </c>
       <c r="M2" s="0">
-        <v>2.7642300269876356</v>
+        <v>2.7427715496764895</v>
       </c>
       <c r="N2" s="0">
-        <v>2.8110315347877406</v>
+        <v>2.7937343258649023</v>
       </c>
     </row>
   </sheetData>
@@ -283,43 +283,43 @@
         <v>46112</v>
       </c>
       <c r="B2" s="0">
-        <v>0.20742596900922691</v>
+        <v>0.20922557220301896</v>
       </c>
       <c r="C2" s="0">
-        <v>0.61624454583293009</v>
+        <v>0.61428005911062866</v>
       </c>
       <c r="D2" s="0">
-        <v>0.88797412455190117</v>
+        <v>0.88952953341362395</v>
       </c>
       <c r="E2" s="0">
-        <v>1.1356814348227451</v>
+        <v>1.1385872182789358</v>
       </c>
       <c r="F2" s="0">
-        <v>1.4179783161389323</v>
+        <v>1.4420069966999818</v>
       </c>
       <c r="G2" s="0">
-        <v>1.2531606842588718</v>
+        <v>1.2730193013704616</v>
       </c>
       <c r="H2" s="0">
-        <v>1.4976329358356775</v>
+        <v>1.5081705556069278</v>
       </c>
       <c r="I2" s="0">
-        <v>1.6541341326219272</v>
+        <v>1.6600008537250881</v>
       </c>
       <c r="J2" s="0">
-        <v>1.7805538881035772</v>
+        <v>1.7917494348483765</v>
       </c>
       <c r="K2" s="0">
-        <v>1.9227269565570251</v>
+        <v>1.9016500614555947</v>
       </c>
       <c r="L2" s="0">
-        <v>1.5456228397773255</v>
+        <v>1.5652776745567292</v>
       </c>
       <c r="M2" s="0">
-        <v>0.8683460805508707</v>
+        <v>0.87412538385316807</v>
       </c>
       <c r="N2" s="0">
-        <v>1.2113733748413091</v>
+        <v>1.2143413184007383</v>
       </c>
     </row>
   </sheetData>
@@ -396,43 +396,43 @@
         <v>46112</v>
       </c>
       <c r="B2" s="0">
-        <v>0.43090756173222056</v>
+        <v>0.34117717339272829</v>
       </c>
       <c r="C2" s="0">
-        <v>0.083119189261146378</v>
+        <v>0.11702381860755069</v>
       </c>
       <c r="D2" s="0">
-        <v>0.73133116293566325</v>
+        <v>0.70202537558147315</v>
       </c>
       <c r="E2" s="0">
-        <v>1.0676002121255035</v>
+        <v>1.0553794312424514</v>
       </c>
       <c r="F2" s="0">
-        <v>1.3132050680056462</v>
+        <v>1.3227492448843972</v>
       </c>
       <c r="G2" s="0">
-        <v>0.63884715733468189</v>
+        <v>0.60671496015620774</v>
       </c>
       <c r="H2" s="0">
-        <v>-1.1079556652577645</v>
+        <v>-1.0824786882163189</v>
       </c>
       <c r="I2" s="0">
-        <v>-1.3191304794171512</v>
+        <v>-1.3185463143649085</v>
       </c>
       <c r="J2" s="0">
-        <v>-1.4618100626276662</v>
+        <v>-1.4769681203826817</v>
       </c>
       <c r="K2" s="0">
-        <v>-2.0993653824937777</v>
+        <v>-2.0647960546479176</v>
       </c>
       <c r="L2" s="0">
-        <v>-2.3049001249939511</v>
+        <v>-2.3051767633175162</v>
       </c>
       <c r="M2" s="0">
-        <v>-0.78807144147115005</v>
+        <v>-0.80873940700948133</v>
       </c>
       <c r="N2" s="0">
-        <v>-1.3306422966182765</v>
+        <v>-1.3468329682167752</v>
       </c>
     </row>
   </sheetData>
